--- a/data/validation/structural/shell/pipes/results/results_for_L_pipe.xlsx
+++ b/data/validation/structural/shell/pipes/results/results_for_L_pipe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\VIBRA\data\validation\structural\shell\pipes\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8BAF01-E3AC-4D80-9596-DC62D7EA8A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216C4788-C71F-4717-A9E0-6B2AABE786BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" xr2:uid="{663DECE1-D11E-44CD-A079-C79636EAEC85}"/>
   </bookViews>
